--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-07.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-07.xlsx
@@ -578,15 +578,19 @@
       <c r="K2" t="n">
         <v>1.25</v>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>AO Home Win</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>GREEN</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>✅ LIQUIDADO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-07.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-07.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,26 +509,6 @@
           <t>Liquidez_Lay</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Hora_Str</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Risco_Red_R$</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Stake_Sugerida_R$</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Lucro_Green_R$</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -578,19 +558,15 @@
       <c r="K2" t="n">
         <v>1.25</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>AO Home Win</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>GREEN</t>
+          <t>PENDENTE</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>✅ LIQUIDADO</t>
+          <t>⏳ PENDENTE</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -600,20 +576,6 @@
       </c>
       <c r="P2" t="n">
         <v>491</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>06:30</t>
-        </is>
-      </c>
-      <c r="R2" t="n">
-        <v>200</v>
-      </c>
-      <c r="S2" t="n">
-        <v>29.41</v>
-      </c>
-      <c r="T2" t="n">
-        <v>28.09</v>
       </c>
     </row>
   </sheetData>

--- a/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-07.xlsx
+++ b/metodos_aprovados/Sinais_Metodos_Aprovados_2026-10-07.xlsx
@@ -561,12 +561,12 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>SEM_PLACAR</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⏳ PENDENTE</t>
+          <t>⚪ SEM_PLACAR</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
